--- a/plantilla-import-productos.xlsx
+++ b/plantilla-import-productos.xlsx
@@ -102,12 +102,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -197,77 +199,87 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIO. Nombre del producto.</t>
+        <t>OBLIGATORIO. Nombre del producto tal como aparece en la gondola / catalogo.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Opcional. Si va vacio se genera automaticamente desde el nombre. Debe ser unico.</t>
+        <t>Opcional. Si se deja vacio se genera automaticamente desde el nombre. Debe ser unico.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Opcional. Descripcion del producto.</t>
+        <t>Codigo de barras EAN-13 (13 digitos) o EAN-8. Columna formateada como TEXTO para no perder ceros a la izquierda. Opcional.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Precio de venta en ARS. Sin separador de miles. Ej: 1800</t>
+        <t>Opcional. Descripcion del producto (aparece en la ficha).</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Costo de compra en ARS.</t>
+        <t>Precio de venta en ARS (sin separador de miles). Ej: 1800</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Stock inicial. Default 100 si va vacio.</t>
+        <t>Costo de compra en ARS.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Stock minimo para alerta. Default 5.</t>
+        <t>Stock inicial. Default 100 si va vacio.</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>Slug de categoria de tienda. Valores validos: hamburguesas, pizzas, sushi, lacteos, bebidas, sandwicheria, golosinas, almacen, limpieza.</t>
+        <t>Stock minimo para alerta. Default 5.</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIO para logistica. Valores: MICRO, SMALL, MEDIUM, LARGE, XL.</t>
+        <t>Slug de categoria de tienda. Valores validos: hamburguesas, pizzas, sushi, lacteos, bebidas, sandwicheria, golosinas, almacen, limpieza.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Peso maximo del paquete en gramos. Informativo.</t>
+        <t>OBLIGATORIO para logistica. Valores: MICRO, SMALL, MEDIUM, LARGE, XL.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Largo maximo en cm. Informativo.</t>
+        <t>Peso maximo del paquete en gramos. Informativo (se hereda del packageCategory).</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Ancho maximo en cm. Informativo.</t>
+        <t>Largo maximo en cm. Informativo.</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>Alto maximo en cm. Informativo.</t>
+        <t>Ancho maximo en cm. Informativo.</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>Score de volumen: MICRO=1, SMALL=3, MEDIUM=6, LARGE=10, XL=20.</t>
+        <t>Alto maximo en cm. Informativo.</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
+        <t>Score de volumen: MICRO=1, SMALL=3, MEDIUM=6, LARGE=10, XL=20.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
         <t>Vehiculos permitidos separados por coma. Ej: BIKE,MOTO,CAR,TRUCK</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>URL publica de la imagen subida a Cloudflare R2. Ej: https://cdn.somosmoovy.com/products/coca-cola-15l.webp  (o https://pub-{ACCOUNT_ID}.r2.dev/{key})</t>
       </text>
     </comment>
   </commentList>
@@ -563,27 +575,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:Q1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="48" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>name</t>
@@ -596,67 +610,77 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>barcode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>costPrice</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>stock</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>minStock</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>categorySlug</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>packageCategory</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>maxWeightGrams</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>maxLengthCm</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>maxWidthCm</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>maxHeightCm</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>volumeScore</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>allowedVehicles</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>imageUrl</t>
         </is>
       </c>
     </row>
@@ -671,476 +695,3067 @@
           <t>coca-cola-15l</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Gaseosa cola 1.5 litros</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>7790895000129</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Gaseosa cola 1.5 litros, botella PET</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
         <v>1800</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="F2" s="2" t="n">
         <v>1200</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="G2" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>bebidas</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>SMALL</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="K2" s="2" t="n">
         <v>2000</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="L2" s="2" t="n">
         <v>35</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="M2" s="2" t="n">
         <v>25</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="N2" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="O2" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>BIKE,MOTO,CAR,TRUCK</t>
         </is>
       </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>https://cdn.somosmoovy.com/products/coca-cola-15l.webp</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Yerba Taragui 1kg</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>yerba-taragui-1kg</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Yerba mate con palo</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>3200</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>almacen</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>SMALL</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>BIKE,MOTO,CAR,TRUCK</t>
-        </is>
-      </c>
+      <c r="C3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Aceite Natura 1.5L</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>aceite-natura-15l</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Aceite de girasol premium</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1900</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>almacen</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>MOTO,CAR,TRUCK</t>
-        </is>
-      </c>
+      <c r="C4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Pack Cerveza Quilmes x6</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>pack-quilmes-x6</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Pack de 6 latas 473ml</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>6500</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>bebidas</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>MOTO,CAR,TRUCK</t>
-        </is>
-      </c>
+      <c r="C5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Papel Higienico Scott x12</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>papel-scott-x12</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Papel doble hoja x12 rollos</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>8500</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6200</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>limpieza</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>LARGE</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="N6" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>CAR,TRUCK</t>
-        </is>
-      </c>
+      <c r="C6" s="4" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Alfajor Havanna</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>alfajor-havanna</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Alfajor de chocolate</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>1500</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>golosinas</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>MICRO</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="K7" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M7" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>BIKE,MOTO,CAR,TRUCK</t>
-        </is>
-      </c>
+      <c r="C7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Tostado Jamon y Queso</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>tostado-jamon-queso</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Tostado clasico</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>sandwicheria</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>MICRO</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>BIKE,MOTO,CAR,TRUCK</t>
-        </is>
-      </c>
+      <c r="C8" s="4" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Queso Cremoso Tregar 1kg</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>queso-tregar-1kg</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Queso cremoso</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>4500</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>lacteos</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>SMALL</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>2000</v>
-      </c>
-      <c r="K9" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>25</v>
-      </c>
-      <c r="M9" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="N9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>BIKE,MOTO,CAR,TRUCK</t>
-        </is>
-      </c>
+      <c r="C9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="C10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="C11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="C12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="C13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="C31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="C32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="C34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="C36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="C37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="C38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="C39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="C40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="C41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="C42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="C43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="C44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="C45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="C46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="C47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="C48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="C49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="C50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="C51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="C52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="C53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="C54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="C55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="C56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="C57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="C58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="C59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="C60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="C61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="C62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="C63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="C64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="C65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="C66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="C67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="C68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="C69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="C70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="C71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="C72" s="4" t="n"/>
+    </row>
+    <row r="73">
+      <c r="C73" s="4" t="n"/>
+    </row>
+    <row r="74">
+      <c r="C74" s="4" t="n"/>
+    </row>
+    <row r="75">
+      <c r="C75" s="4" t="n"/>
+    </row>
+    <row r="76">
+      <c r="C76" s="4" t="n"/>
+    </row>
+    <row r="77">
+      <c r="C77" s="4" t="n"/>
+    </row>
+    <row r="78">
+      <c r="C78" s="4" t="n"/>
+    </row>
+    <row r="79">
+      <c r="C79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="C80" s="4" t="n"/>
+    </row>
+    <row r="81">
+      <c r="C81" s="4" t="n"/>
+    </row>
+    <row r="82">
+      <c r="C82" s="4" t="n"/>
+    </row>
+    <row r="83">
+      <c r="C83" s="4" t="n"/>
+    </row>
+    <row r="84">
+      <c r="C84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="C85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="C86" s="4" t="n"/>
+    </row>
+    <row r="87">
+      <c r="C87" s="4" t="n"/>
+    </row>
+    <row r="88">
+      <c r="C88" s="4" t="n"/>
+    </row>
+    <row r="89">
+      <c r="C89" s="4" t="n"/>
+    </row>
+    <row r="90">
+      <c r="C90" s="4" t="n"/>
+    </row>
+    <row r="91">
+      <c r="C91" s="4" t="n"/>
+    </row>
+    <row r="92">
+      <c r="C92" s="4" t="n"/>
+    </row>
+    <row r="93">
+      <c r="C93" s="4" t="n"/>
+    </row>
+    <row r="94">
+      <c r="C94" s="4" t="n"/>
+    </row>
+    <row r="95">
+      <c r="C95" s="4" t="n"/>
+    </row>
+    <row r="96">
+      <c r="C96" s="4" t="n"/>
+    </row>
+    <row r="97">
+      <c r="C97" s="4" t="n"/>
+    </row>
+    <row r="98">
+      <c r="C98" s="4" t="n"/>
+    </row>
+    <row r="99">
+      <c r="C99" s="4" t="n"/>
+    </row>
+    <row r="100">
+      <c r="C100" s="4" t="n"/>
+    </row>
+    <row r="101">
+      <c r="C101" s="4" t="n"/>
+    </row>
+    <row r="102">
+      <c r="C102" s="4" t="n"/>
+    </row>
+    <row r="103">
+      <c r="C103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="C104" s="4" t="n"/>
+    </row>
+    <row r="105">
+      <c r="C105" s="4" t="n"/>
+    </row>
+    <row r="106">
+      <c r="C106" s="4" t="n"/>
+    </row>
+    <row r="107">
+      <c r="C107" s="4" t="n"/>
+    </row>
+    <row r="108">
+      <c r="C108" s="4" t="n"/>
+    </row>
+    <row r="109">
+      <c r="C109" s="4" t="n"/>
+    </row>
+    <row r="110">
+      <c r="C110" s="4" t="n"/>
+    </row>
+    <row r="111">
+      <c r="C111" s="4" t="n"/>
+    </row>
+    <row r="112">
+      <c r="C112" s="4" t="n"/>
+    </row>
+    <row r="113">
+      <c r="C113" s="4" t="n"/>
+    </row>
+    <row r="114">
+      <c r="C114" s="4" t="n"/>
+    </row>
+    <row r="115">
+      <c r="C115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="C116" s="4" t="n"/>
+    </row>
+    <row r="117">
+      <c r="C117" s="4" t="n"/>
+    </row>
+    <row r="118">
+      <c r="C118" s="4" t="n"/>
+    </row>
+    <row r="119">
+      <c r="C119" s="4" t="n"/>
+    </row>
+    <row r="120">
+      <c r="C120" s="4" t="n"/>
+    </row>
+    <row r="121">
+      <c r="C121" s="4" t="n"/>
+    </row>
+    <row r="122">
+      <c r="C122" s="4" t="n"/>
+    </row>
+    <row r="123">
+      <c r="C123" s="4" t="n"/>
+    </row>
+    <row r="124">
+      <c r="C124" s="4" t="n"/>
+    </row>
+    <row r="125">
+      <c r="C125" s="4" t="n"/>
+    </row>
+    <row r="126">
+      <c r="C126" s="4" t="n"/>
+    </row>
+    <row r="127">
+      <c r="C127" s="4" t="n"/>
+    </row>
+    <row r="128">
+      <c r="C128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="C129" s="4" t="n"/>
+    </row>
+    <row r="130">
+      <c r="C130" s="4" t="n"/>
+    </row>
+    <row r="131">
+      <c r="C131" s="4" t="n"/>
+    </row>
+    <row r="132">
+      <c r="C132" s="4" t="n"/>
+    </row>
+    <row r="133">
+      <c r="C133" s="4" t="n"/>
+    </row>
+    <row r="134">
+      <c r="C134" s="4" t="n"/>
+    </row>
+    <row r="135">
+      <c r="C135" s="4" t="n"/>
+    </row>
+    <row r="136">
+      <c r="C136" s="4" t="n"/>
+    </row>
+    <row r="137">
+      <c r="C137" s="4" t="n"/>
+    </row>
+    <row r="138">
+      <c r="C138" s="4" t="n"/>
+    </row>
+    <row r="139">
+      <c r="C139" s="4" t="n"/>
+    </row>
+    <row r="140">
+      <c r="C140" s="4" t="n"/>
+    </row>
+    <row r="141">
+      <c r="C141" s="4" t="n"/>
+    </row>
+    <row r="142">
+      <c r="C142" s="4" t="n"/>
+    </row>
+    <row r="143">
+      <c r="C143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="C144" s="4" t="n"/>
+    </row>
+    <row r="145">
+      <c r="C145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="C146" s="4" t="n"/>
+    </row>
+    <row r="147">
+      <c r="C147" s="4" t="n"/>
+    </row>
+    <row r="148">
+      <c r="C148" s="4" t="n"/>
+    </row>
+    <row r="149">
+      <c r="C149" s="4" t="n"/>
+    </row>
+    <row r="150">
+      <c r="C150" s="4" t="n"/>
+    </row>
+    <row r="151">
+      <c r="C151" s="4" t="n"/>
+    </row>
+    <row r="152">
+      <c r="C152" s="4" t="n"/>
+    </row>
+    <row r="153">
+      <c r="C153" s="4" t="n"/>
+    </row>
+    <row r="154">
+      <c r="C154" s="4" t="n"/>
+    </row>
+    <row r="155">
+      <c r="C155" s="4" t="n"/>
+    </row>
+    <row r="156">
+      <c r="C156" s="4" t="n"/>
+    </row>
+    <row r="157">
+      <c r="C157" s="4" t="n"/>
+    </row>
+    <row r="158">
+      <c r="C158" s="4" t="n"/>
+    </row>
+    <row r="159">
+      <c r="C159" s="4" t="n"/>
+    </row>
+    <row r="160">
+      <c r="C160" s="4" t="n"/>
+    </row>
+    <row r="161">
+      <c r="C161" s="4" t="n"/>
+    </row>
+    <row r="162">
+      <c r="C162" s="4" t="n"/>
+    </row>
+    <row r="163">
+      <c r="C163" s="4" t="n"/>
+    </row>
+    <row r="164">
+      <c r="C164" s="4" t="n"/>
+    </row>
+    <row r="165">
+      <c r="C165" s="4" t="n"/>
+    </row>
+    <row r="166">
+      <c r="C166" s="4" t="n"/>
+    </row>
+    <row r="167">
+      <c r="C167" s="4" t="n"/>
+    </row>
+    <row r="168">
+      <c r="C168" s="4" t="n"/>
+    </row>
+    <row r="169">
+      <c r="C169" s="4" t="n"/>
+    </row>
+    <row r="170">
+      <c r="C170" s="4" t="n"/>
+    </row>
+    <row r="171">
+      <c r="C171" s="4" t="n"/>
+    </row>
+    <row r="172">
+      <c r="C172" s="4" t="n"/>
+    </row>
+    <row r="173">
+      <c r="C173" s="4" t="n"/>
+    </row>
+    <row r="174">
+      <c r="C174" s="4" t="n"/>
+    </row>
+    <row r="175">
+      <c r="C175" s="4" t="n"/>
+    </row>
+    <row r="176">
+      <c r="C176" s="4" t="n"/>
+    </row>
+    <row r="177">
+      <c r="C177" s="4" t="n"/>
+    </row>
+    <row r="178">
+      <c r="C178" s="4" t="n"/>
+    </row>
+    <row r="179">
+      <c r="C179" s="4" t="n"/>
+    </row>
+    <row r="180">
+      <c r="C180" s="4" t="n"/>
+    </row>
+    <row r="181">
+      <c r="C181" s="4" t="n"/>
+    </row>
+    <row r="182">
+      <c r="C182" s="4" t="n"/>
+    </row>
+    <row r="183">
+      <c r="C183" s="4" t="n"/>
+    </row>
+    <row r="184">
+      <c r="C184" s="4" t="n"/>
+    </row>
+    <row r="185">
+      <c r="C185" s="4" t="n"/>
+    </row>
+    <row r="186">
+      <c r="C186" s="4" t="n"/>
+    </row>
+    <row r="187">
+      <c r="C187" s="4" t="n"/>
+    </row>
+    <row r="188">
+      <c r="C188" s="4" t="n"/>
+    </row>
+    <row r="189">
+      <c r="C189" s="4" t="n"/>
+    </row>
+    <row r="190">
+      <c r="C190" s="4" t="n"/>
+    </row>
+    <row r="191">
+      <c r="C191" s="4" t="n"/>
+    </row>
+    <row r="192">
+      <c r="C192" s="4" t="n"/>
+    </row>
+    <row r="193">
+      <c r="C193" s="4" t="n"/>
+    </row>
+    <row r="194">
+      <c r="C194" s="4" t="n"/>
+    </row>
+    <row r="195">
+      <c r="C195" s="4" t="n"/>
+    </row>
+    <row r="196">
+      <c r="C196" s="4" t="n"/>
+    </row>
+    <row r="197">
+      <c r="C197" s="4" t="n"/>
+    </row>
+    <row r="198">
+      <c r="C198" s="4" t="n"/>
+    </row>
+    <row r="199">
+      <c r="C199" s="4" t="n"/>
+    </row>
+    <row r="200">
+      <c r="C200" s="4" t="n"/>
+    </row>
+    <row r="201">
+      <c r="C201" s="4" t="n"/>
+    </row>
+    <row r="202">
+      <c r="C202" s="4" t="n"/>
+    </row>
+    <row r="203">
+      <c r="C203" s="4" t="n"/>
+    </row>
+    <row r="204">
+      <c r="C204" s="4" t="n"/>
+    </row>
+    <row r="205">
+      <c r="C205" s="4" t="n"/>
+    </row>
+    <row r="206">
+      <c r="C206" s="4" t="n"/>
+    </row>
+    <row r="207">
+      <c r="C207" s="4" t="n"/>
+    </row>
+    <row r="208">
+      <c r="C208" s="4" t="n"/>
+    </row>
+    <row r="209">
+      <c r="C209" s="4" t="n"/>
+    </row>
+    <row r="210">
+      <c r="C210" s="4" t="n"/>
+    </row>
+    <row r="211">
+      <c r="C211" s="4" t="n"/>
+    </row>
+    <row r="212">
+      <c r="C212" s="4" t="n"/>
+    </row>
+    <row r="213">
+      <c r="C213" s="4" t="n"/>
+    </row>
+    <row r="214">
+      <c r="C214" s="4" t="n"/>
+    </row>
+    <row r="215">
+      <c r="C215" s="4" t="n"/>
+    </row>
+    <row r="216">
+      <c r="C216" s="4" t="n"/>
+    </row>
+    <row r="217">
+      <c r="C217" s="4" t="n"/>
+    </row>
+    <row r="218">
+      <c r="C218" s="4" t="n"/>
+    </row>
+    <row r="219">
+      <c r="C219" s="4" t="n"/>
+    </row>
+    <row r="220">
+      <c r="C220" s="4" t="n"/>
+    </row>
+    <row r="221">
+      <c r="C221" s="4" t="n"/>
+    </row>
+    <row r="222">
+      <c r="C222" s="4" t="n"/>
+    </row>
+    <row r="223">
+      <c r="C223" s="4" t="n"/>
+    </row>
+    <row r="224">
+      <c r="C224" s="4" t="n"/>
+    </row>
+    <row r="225">
+      <c r="C225" s="4" t="n"/>
+    </row>
+    <row r="226">
+      <c r="C226" s="4" t="n"/>
+    </row>
+    <row r="227">
+      <c r="C227" s="4" t="n"/>
+    </row>
+    <row r="228">
+      <c r="C228" s="4" t="n"/>
+    </row>
+    <row r="229">
+      <c r="C229" s="4" t="n"/>
+    </row>
+    <row r="230">
+      <c r="C230" s="4" t="n"/>
+    </row>
+    <row r="231">
+      <c r="C231" s="4" t="n"/>
+    </row>
+    <row r="232">
+      <c r="C232" s="4" t="n"/>
+    </row>
+    <row r="233">
+      <c r="C233" s="4" t="n"/>
+    </row>
+    <row r="234">
+      <c r="C234" s="4" t="n"/>
+    </row>
+    <row r="235">
+      <c r="C235" s="4" t="n"/>
+    </row>
+    <row r="236">
+      <c r="C236" s="4" t="n"/>
+    </row>
+    <row r="237">
+      <c r="C237" s="4" t="n"/>
+    </row>
+    <row r="238">
+      <c r="C238" s="4" t="n"/>
+    </row>
+    <row r="239">
+      <c r="C239" s="4" t="n"/>
+    </row>
+    <row r="240">
+      <c r="C240" s="4" t="n"/>
+    </row>
+    <row r="241">
+      <c r="C241" s="4" t="n"/>
+    </row>
+    <row r="242">
+      <c r="C242" s="4" t="n"/>
+    </row>
+    <row r="243">
+      <c r="C243" s="4" t="n"/>
+    </row>
+    <row r="244">
+      <c r="C244" s="4" t="n"/>
+    </row>
+    <row r="245">
+      <c r="C245" s="4" t="n"/>
+    </row>
+    <row r="246">
+      <c r="C246" s="4" t="n"/>
+    </row>
+    <row r="247">
+      <c r="C247" s="4" t="n"/>
+    </row>
+    <row r="248">
+      <c r="C248" s="4" t="n"/>
+    </row>
+    <row r="249">
+      <c r="C249" s="4" t="n"/>
+    </row>
+    <row r="250">
+      <c r="C250" s="4" t="n"/>
+    </row>
+    <row r="251">
+      <c r="C251" s="4" t="n"/>
+    </row>
+    <row r="252">
+      <c r="C252" s="4" t="n"/>
+    </row>
+    <row r="253">
+      <c r="C253" s="4" t="n"/>
+    </row>
+    <row r="254">
+      <c r="C254" s="4" t="n"/>
+    </row>
+    <row r="255">
+      <c r="C255" s="4" t="n"/>
+    </row>
+    <row r="256">
+      <c r="C256" s="4" t="n"/>
+    </row>
+    <row r="257">
+      <c r="C257" s="4" t="n"/>
+    </row>
+    <row r="258">
+      <c r="C258" s="4" t="n"/>
+    </row>
+    <row r="259">
+      <c r="C259" s="4" t="n"/>
+    </row>
+    <row r="260">
+      <c r="C260" s="4" t="n"/>
+    </row>
+    <row r="261">
+      <c r="C261" s="4" t="n"/>
+    </row>
+    <row r="262">
+      <c r="C262" s="4" t="n"/>
+    </row>
+    <row r="263">
+      <c r="C263" s="4" t="n"/>
+    </row>
+    <row r="264">
+      <c r="C264" s="4" t="n"/>
+    </row>
+    <row r="265">
+      <c r="C265" s="4" t="n"/>
+    </row>
+    <row r="266">
+      <c r="C266" s="4" t="n"/>
+    </row>
+    <row r="267">
+      <c r="C267" s="4" t="n"/>
+    </row>
+    <row r="268">
+      <c r="C268" s="4" t="n"/>
+    </row>
+    <row r="269">
+      <c r="C269" s="4" t="n"/>
+    </row>
+    <row r="270">
+      <c r="C270" s="4" t="n"/>
+    </row>
+    <row r="271">
+      <c r="C271" s="4" t="n"/>
+    </row>
+    <row r="272">
+      <c r="C272" s="4" t="n"/>
+    </row>
+    <row r="273">
+      <c r="C273" s="4" t="n"/>
+    </row>
+    <row r="274">
+      <c r="C274" s="4" t="n"/>
+    </row>
+    <row r="275">
+      <c r="C275" s="4" t="n"/>
+    </row>
+    <row r="276">
+      <c r="C276" s="4" t="n"/>
+    </row>
+    <row r="277">
+      <c r="C277" s="4" t="n"/>
+    </row>
+    <row r="278">
+      <c r="C278" s="4" t="n"/>
+    </row>
+    <row r="279">
+      <c r="C279" s="4" t="n"/>
+    </row>
+    <row r="280">
+      <c r="C280" s="4" t="n"/>
+    </row>
+    <row r="281">
+      <c r="C281" s="4" t="n"/>
+    </row>
+    <row r="282">
+      <c r="C282" s="4" t="n"/>
+    </row>
+    <row r="283">
+      <c r="C283" s="4" t="n"/>
+    </row>
+    <row r="284">
+      <c r="C284" s="4" t="n"/>
+    </row>
+    <row r="285">
+      <c r="C285" s="4" t="n"/>
+    </row>
+    <row r="286">
+      <c r="C286" s="4" t="n"/>
+    </row>
+    <row r="287">
+      <c r="C287" s="4" t="n"/>
+    </row>
+    <row r="288">
+      <c r="C288" s="4" t="n"/>
+    </row>
+    <row r="289">
+      <c r="C289" s="4" t="n"/>
+    </row>
+    <row r="290">
+      <c r="C290" s="4" t="n"/>
+    </row>
+    <row r="291">
+      <c r="C291" s="4" t="n"/>
+    </row>
+    <row r="292">
+      <c r="C292" s="4" t="n"/>
+    </row>
+    <row r="293">
+      <c r="C293" s="4" t="n"/>
+    </row>
+    <row r="294">
+      <c r="C294" s="4" t="n"/>
+    </row>
+    <row r="295">
+      <c r="C295" s="4" t="n"/>
+    </row>
+    <row r="296">
+      <c r="C296" s="4" t="n"/>
+    </row>
+    <row r="297">
+      <c r="C297" s="4" t="n"/>
+    </row>
+    <row r="298">
+      <c r="C298" s="4" t="n"/>
+    </row>
+    <row r="299">
+      <c r="C299" s="4" t="n"/>
+    </row>
+    <row r="300">
+      <c r="C300" s="4" t="n"/>
+    </row>
+    <row r="301">
+      <c r="C301" s="4" t="n"/>
+    </row>
+    <row r="302">
+      <c r="C302" s="4" t="n"/>
+    </row>
+    <row r="303">
+      <c r="C303" s="4" t="n"/>
+    </row>
+    <row r="304">
+      <c r="C304" s="4" t="n"/>
+    </row>
+    <row r="305">
+      <c r="C305" s="4" t="n"/>
+    </row>
+    <row r="306">
+      <c r="C306" s="4" t="n"/>
+    </row>
+    <row r="307">
+      <c r="C307" s="4" t="n"/>
+    </row>
+    <row r="308">
+      <c r="C308" s="4" t="n"/>
+    </row>
+    <row r="309">
+      <c r="C309" s="4" t="n"/>
+    </row>
+    <row r="310">
+      <c r="C310" s="4" t="n"/>
+    </row>
+    <row r="311">
+      <c r="C311" s="4" t="n"/>
+    </row>
+    <row r="312">
+      <c r="C312" s="4" t="n"/>
+    </row>
+    <row r="313">
+      <c r="C313" s="4" t="n"/>
+    </row>
+    <row r="314">
+      <c r="C314" s="4" t="n"/>
+    </row>
+    <row r="315">
+      <c r="C315" s="4" t="n"/>
+    </row>
+    <row r="316">
+      <c r="C316" s="4" t="n"/>
+    </row>
+    <row r="317">
+      <c r="C317" s="4" t="n"/>
+    </row>
+    <row r="318">
+      <c r="C318" s="4" t="n"/>
+    </row>
+    <row r="319">
+      <c r="C319" s="4" t="n"/>
+    </row>
+    <row r="320">
+      <c r="C320" s="4" t="n"/>
+    </row>
+    <row r="321">
+      <c r="C321" s="4" t="n"/>
+    </row>
+    <row r="322">
+      <c r="C322" s="4" t="n"/>
+    </row>
+    <row r="323">
+      <c r="C323" s="4" t="n"/>
+    </row>
+    <row r="324">
+      <c r="C324" s="4" t="n"/>
+    </row>
+    <row r="325">
+      <c r="C325" s="4" t="n"/>
+    </row>
+    <row r="326">
+      <c r="C326" s="4" t="n"/>
+    </row>
+    <row r="327">
+      <c r="C327" s="4" t="n"/>
+    </row>
+    <row r="328">
+      <c r="C328" s="4" t="n"/>
+    </row>
+    <row r="329">
+      <c r="C329" s="4" t="n"/>
+    </row>
+    <row r="330">
+      <c r="C330" s="4" t="n"/>
+    </row>
+    <row r="331">
+      <c r="C331" s="4" t="n"/>
+    </row>
+    <row r="332">
+      <c r="C332" s="4" t="n"/>
+    </row>
+    <row r="333">
+      <c r="C333" s="4" t="n"/>
+    </row>
+    <row r="334">
+      <c r="C334" s="4" t="n"/>
+    </row>
+    <row r="335">
+      <c r="C335" s="4" t="n"/>
+    </row>
+    <row r="336">
+      <c r="C336" s="4" t="n"/>
+    </row>
+    <row r="337">
+      <c r="C337" s="4" t="n"/>
+    </row>
+    <row r="338">
+      <c r="C338" s="4" t="n"/>
+    </row>
+    <row r="339">
+      <c r="C339" s="4" t="n"/>
+    </row>
+    <row r="340">
+      <c r="C340" s="4" t="n"/>
+    </row>
+    <row r="341">
+      <c r="C341" s="4" t="n"/>
+    </row>
+    <row r="342">
+      <c r="C342" s="4" t="n"/>
+    </row>
+    <row r="343">
+      <c r="C343" s="4" t="n"/>
+    </row>
+    <row r="344">
+      <c r="C344" s="4" t="n"/>
+    </row>
+    <row r="345">
+      <c r="C345" s="4" t="n"/>
+    </row>
+    <row r="346">
+      <c r="C346" s="4" t="n"/>
+    </row>
+    <row r="347">
+      <c r="C347" s="4" t="n"/>
+    </row>
+    <row r="348">
+      <c r="C348" s="4" t="n"/>
+    </row>
+    <row r="349">
+      <c r="C349" s="4" t="n"/>
+    </row>
+    <row r="350">
+      <c r="C350" s="4" t="n"/>
+    </row>
+    <row r="351">
+      <c r="C351" s="4" t="n"/>
+    </row>
+    <row r="352">
+      <c r="C352" s="4" t="n"/>
+    </row>
+    <row r="353">
+      <c r="C353" s="4" t="n"/>
+    </row>
+    <row r="354">
+      <c r="C354" s="4" t="n"/>
+    </row>
+    <row r="355">
+      <c r="C355" s="4" t="n"/>
+    </row>
+    <row r="356">
+      <c r="C356" s="4" t="n"/>
+    </row>
+    <row r="357">
+      <c r="C357" s="4" t="n"/>
+    </row>
+    <row r="358">
+      <c r="C358" s="4" t="n"/>
+    </row>
+    <row r="359">
+      <c r="C359" s="4" t="n"/>
+    </row>
+    <row r="360">
+      <c r="C360" s="4" t="n"/>
+    </row>
+    <row r="361">
+      <c r="C361" s="4" t="n"/>
+    </row>
+    <row r="362">
+      <c r="C362" s="4" t="n"/>
+    </row>
+    <row r="363">
+      <c r="C363" s="4" t="n"/>
+    </row>
+    <row r="364">
+      <c r="C364" s="4" t="n"/>
+    </row>
+    <row r="365">
+      <c r="C365" s="4" t="n"/>
+    </row>
+    <row r="366">
+      <c r="C366" s="4" t="n"/>
+    </row>
+    <row r="367">
+      <c r="C367" s="4" t="n"/>
+    </row>
+    <row r="368">
+      <c r="C368" s="4" t="n"/>
+    </row>
+    <row r="369">
+      <c r="C369" s="4" t="n"/>
+    </row>
+    <row r="370">
+      <c r="C370" s="4" t="n"/>
+    </row>
+    <row r="371">
+      <c r="C371" s="4" t="n"/>
+    </row>
+    <row r="372">
+      <c r="C372" s="4" t="n"/>
+    </row>
+    <row r="373">
+      <c r="C373" s="4" t="n"/>
+    </row>
+    <row r="374">
+      <c r="C374" s="4" t="n"/>
+    </row>
+    <row r="375">
+      <c r="C375" s="4" t="n"/>
+    </row>
+    <row r="376">
+      <c r="C376" s="4" t="n"/>
+    </row>
+    <row r="377">
+      <c r="C377" s="4" t="n"/>
+    </row>
+    <row r="378">
+      <c r="C378" s="4" t="n"/>
+    </row>
+    <row r="379">
+      <c r="C379" s="4" t="n"/>
+    </row>
+    <row r="380">
+      <c r="C380" s="4" t="n"/>
+    </row>
+    <row r="381">
+      <c r="C381" s="4" t="n"/>
+    </row>
+    <row r="382">
+      <c r="C382" s="4" t="n"/>
+    </row>
+    <row r="383">
+      <c r="C383" s="4" t="n"/>
+    </row>
+    <row r="384">
+      <c r="C384" s="4" t="n"/>
+    </row>
+    <row r="385">
+      <c r="C385" s="4" t="n"/>
+    </row>
+    <row r="386">
+      <c r="C386" s="4" t="n"/>
+    </row>
+    <row r="387">
+      <c r="C387" s="4" t="n"/>
+    </row>
+    <row r="388">
+      <c r="C388" s="4" t="n"/>
+    </row>
+    <row r="389">
+      <c r="C389" s="4" t="n"/>
+    </row>
+    <row r="390">
+      <c r="C390" s="4" t="n"/>
+    </row>
+    <row r="391">
+      <c r="C391" s="4" t="n"/>
+    </row>
+    <row r="392">
+      <c r="C392" s="4" t="n"/>
+    </row>
+    <row r="393">
+      <c r="C393" s="4" t="n"/>
+    </row>
+    <row r="394">
+      <c r="C394" s="4" t="n"/>
+    </row>
+    <row r="395">
+      <c r="C395" s="4" t="n"/>
+    </row>
+    <row r="396">
+      <c r="C396" s="4" t="n"/>
+    </row>
+    <row r="397">
+      <c r="C397" s="4" t="n"/>
+    </row>
+    <row r="398">
+      <c r="C398" s="4" t="n"/>
+    </row>
+    <row r="399">
+      <c r="C399" s="4" t="n"/>
+    </row>
+    <row r="400">
+      <c r="C400" s="4" t="n"/>
+    </row>
+    <row r="401">
+      <c r="C401" s="4" t="n"/>
+    </row>
+    <row r="402">
+      <c r="C402" s="4" t="n"/>
+    </row>
+    <row r="403">
+      <c r="C403" s="4" t="n"/>
+    </row>
+    <row r="404">
+      <c r="C404" s="4" t="n"/>
+    </row>
+    <row r="405">
+      <c r="C405" s="4" t="n"/>
+    </row>
+    <row r="406">
+      <c r="C406" s="4" t="n"/>
+    </row>
+    <row r="407">
+      <c r="C407" s="4" t="n"/>
+    </row>
+    <row r="408">
+      <c r="C408" s="4" t="n"/>
+    </row>
+    <row r="409">
+      <c r="C409" s="4" t="n"/>
+    </row>
+    <row r="410">
+      <c r="C410" s="4" t="n"/>
+    </row>
+    <row r="411">
+      <c r="C411" s="4" t="n"/>
+    </row>
+    <row r="412">
+      <c r="C412" s="4" t="n"/>
+    </row>
+    <row r="413">
+      <c r="C413" s="4" t="n"/>
+    </row>
+    <row r="414">
+      <c r="C414" s="4" t="n"/>
+    </row>
+    <row r="415">
+      <c r="C415" s="4" t="n"/>
+    </row>
+    <row r="416">
+      <c r="C416" s="4" t="n"/>
+    </row>
+    <row r="417">
+      <c r="C417" s="4" t="n"/>
+    </row>
+    <row r="418">
+      <c r="C418" s="4" t="n"/>
+    </row>
+    <row r="419">
+      <c r="C419" s="4" t="n"/>
+    </row>
+    <row r="420">
+      <c r="C420" s="4" t="n"/>
+    </row>
+    <row r="421">
+      <c r="C421" s="4" t="n"/>
+    </row>
+    <row r="422">
+      <c r="C422" s="4" t="n"/>
+    </row>
+    <row r="423">
+      <c r="C423" s="4" t="n"/>
+    </row>
+    <row r="424">
+      <c r="C424" s="4" t="n"/>
+    </row>
+    <row r="425">
+      <c r="C425" s="4" t="n"/>
+    </row>
+    <row r="426">
+      <c r="C426" s="4" t="n"/>
+    </row>
+    <row r="427">
+      <c r="C427" s="4" t="n"/>
+    </row>
+    <row r="428">
+      <c r="C428" s="4" t="n"/>
+    </row>
+    <row r="429">
+      <c r="C429" s="4" t="n"/>
+    </row>
+    <row r="430">
+      <c r="C430" s="4" t="n"/>
+    </row>
+    <row r="431">
+      <c r="C431" s="4" t="n"/>
+    </row>
+    <row r="432">
+      <c r="C432" s="4" t="n"/>
+    </row>
+    <row r="433">
+      <c r="C433" s="4" t="n"/>
+    </row>
+    <row r="434">
+      <c r="C434" s="4" t="n"/>
+    </row>
+    <row r="435">
+      <c r="C435" s="4" t="n"/>
+    </row>
+    <row r="436">
+      <c r="C436" s="4" t="n"/>
+    </row>
+    <row r="437">
+      <c r="C437" s="4" t="n"/>
+    </row>
+    <row r="438">
+      <c r="C438" s="4" t="n"/>
+    </row>
+    <row r="439">
+      <c r="C439" s="4" t="n"/>
+    </row>
+    <row r="440">
+      <c r="C440" s="4" t="n"/>
+    </row>
+    <row r="441">
+      <c r="C441" s="4" t="n"/>
+    </row>
+    <row r="442">
+      <c r="C442" s="4" t="n"/>
+    </row>
+    <row r="443">
+      <c r="C443" s="4" t="n"/>
+    </row>
+    <row r="444">
+      <c r="C444" s="4" t="n"/>
+    </row>
+    <row r="445">
+      <c r="C445" s="4" t="n"/>
+    </row>
+    <row r="446">
+      <c r="C446" s="4" t="n"/>
+    </row>
+    <row r="447">
+      <c r="C447" s="4" t="n"/>
+    </row>
+    <row r="448">
+      <c r="C448" s="4" t="n"/>
+    </row>
+    <row r="449">
+      <c r="C449" s="4" t="n"/>
+    </row>
+    <row r="450">
+      <c r="C450" s="4" t="n"/>
+    </row>
+    <row r="451">
+      <c r="C451" s="4" t="n"/>
+    </row>
+    <row r="452">
+      <c r="C452" s="4" t="n"/>
+    </row>
+    <row r="453">
+      <c r="C453" s="4" t="n"/>
+    </row>
+    <row r="454">
+      <c r="C454" s="4" t="n"/>
+    </row>
+    <row r="455">
+      <c r="C455" s="4" t="n"/>
+    </row>
+    <row r="456">
+      <c r="C456" s="4" t="n"/>
+    </row>
+    <row r="457">
+      <c r="C457" s="4" t="n"/>
+    </row>
+    <row r="458">
+      <c r="C458" s="4" t="n"/>
+    </row>
+    <row r="459">
+      <c r="C459" s="4" t="n"/>
+    </row>
+    <row r="460">
+      <c r="C460" s="4" t="n"/>
+    </row>
+    <row r="461">
+      <c r="C461" s="4" t="n"/>
+    </row>
+    <row r="462">
+      <c r="C462" s="4" t="n"/>
+    </row>
+    <row r="463">
+      <c r="C463" s="4" t="n"/>
+    </row>
+    <row r="464">
+      <c r="C464" s="4" t="n"/>
+    </row>
+    <row r="465">
+      <c r="C465" s="4" t="n"/>
+    </row>
+    <row r="466">
+      <c r="C466" s="4" t="n"/>
+    </row>
+    <row r="467">
+      <c r="C467" s="4" t="n"/>
+    </row>
+    <row r="468">
+      <c r="C468" s="4" t="n"/>
+    </row>
+    <row r="469">
+      <c r="C469" s="4" t="n"/>
+    </row>
+    <row r="470">
+      <c r="C470" s="4" t="n"/>
+    </row>
+    <row r="471">
+      <c r="C471" s="4" t="n"/>
+    </row>
+    <row r="472">
+      <c r="C472" s="4" t="n"/>
+    </row>
+    <row r="473">
+      <c r="C473" s="4" t="n"/>
+    </row>
+    <row r="474">
+      <c r="C474" s="4" t="n"/>
+    </row>
+    <row r="475">
+      <c r="C475" s="4" t="n"/>
+    </row>
+    <row r="476">
+      <c r="C476" s="4" t="n"/>
+    </row>
+    <row r="477">
+      <c r="C477" s="4" t="n"/>
+    </row>
+    <row r="478">
+      <c r="C478" s="4" t="n"/>
+    </row>
+    <row r="479">
+      <c r="C479" s="4" t="n"/>
+    </row>
+    <row r="480">
+      <c r="C480" s="4" t="n"/>
+    </row>
+    <row r="481">
+      <c r="C481" s="4" t="n"/>
+    </row>
+    <row r="482">
+      <c r="C482" s="4" t="n"/>
+    </row>
+    <row r="483">
+      <c r="C483" s="4" t="n"/>
+    </row>
+    <row r="484">
+      <c r="C484" s="4" t="n"/>
+    </row>
+    <row r="485">
+      <c r="C485" s="4" t="n"/>
+    </row>
+    <row r="486">
+      <c r="C486" s="4" t="n"/>
+    </row>
+    <row r="487">
+      <c r="C487" s="4" t="n"/>
+    </row>
+    <row r="488">
+      <c r="C488" s="4" t="n"/>
+    </row>
+    <row r="489">
+      <c r="C489" s="4" t="n"/>
+    </row>
+    <row r="490">
+      <c r="C490" s="4" t="n"/>
+    </row>
+    <row r="491">
+      <c r="C491" s="4" t="n"/>
+    </row>
+    <row r="492">
+      <c r="C492" s="4" t="n"/>
+    </row>
+    <row r="493">
+      <c r="C493" s="4" t="n"/>
+    </row>
+    <row r="494">
+      <c r="C494" s="4" t="n"/>
+    </row>
+    <row r="495">
+      <c r="C495" s="4" t="n"/>
+    </row>
+    <row r="496">
+      <c r="C496" s="4" t="n"/>
+    </row>
+    <row r="497">
+      <c r="C497" s="4" t="n"/>
+    </row>
+    <row r="498">
+      <c r="C498" s="4" t="n"/>
+    </row>
+    <row r="499">
+      <c r="C499" s="4" t="n"/>
+    </row>
+    <row r="500">
+      <c r="C500" s="4" t="n"/>
+    </row>
+    <row r="501">
+      <c r="C501" s="4" t="n"/>
+    </row>
+    <row r="502">
+      <c r="C502" s="4" t="n"/>
+    </row>
+    <row r="503">
+      <c r="C503" s="4" t="n"/>
+    </row>
+    <row r="504">
+      <c r="C504" s="4" t="n"/>
+    </row>
+    <row r="505">
+      <c r="C505" s="4" t="n"/>
+    </row>
+    <row r="506">
+      <c r="C506" s="4" t="n"/>
+    </row>
+    <row r="507">
+      <c r="C507" s="4" t="n"/>
+    </row>
+    <row r="508">
+      <c r="C508" s="4" t="n"/>
+    </row>
+    <row r="509">
+      <c r="C509" s="4" t="n"/>
+    </row>
+    <row r="510">
+      <c r="C510" s="4" t="n"/>
+    </row>
+    <row r="511">
+      <c r="C511" s="4" t="n"/>
+    </row>
+    <row r="512">
+      <c r="C512" s="4" t="n"/>
+    </row>
+    <row r="513">
+      <c r="C513" s="4" t="n"/>
+    </row>
+    <row r="514">
+      <c r="C514" s="4" t="n"/>
+    </row>
+    <row r="515">
+      <c r="C515" s="4" t="n"/>
+    </row>
+    <row r="516">
+      <c r="C516" s="4" t="n"/>
+    </row>
+    <row r="517">
+      <c r="C517" s="4" t="n"/>
+    </row>
+    <row r="518">
+      <c r="C518" s="4" t="n"/>
+    </row>
+    <row r="519">
+      <c r="C519" s="4" t="n"/>
+    </row>
+    <row r="520">
+      <c r="C520" s="4" t="n"/>
+    </row>
+    <row r="521">
+      <c r="C521" s="4" t="n"/>
+    </row>
+    <row r="522">
+      <c r="C522" s="4" t="n"/>
+    </row>
+    <row r="523">
+      <c r="C523" s="4" t="n"/>
+    </row>
+    <row r="524">
+      <c r="C524" s="4" t="n"/>
+    </row>
+    <row r="525">
+      <c r="C525" s="4" t="n"/>
+    </row>
+    <row r="526">
+      <c r="C526" s="4" t="n"/>
+    </row>
+    <row r="527">
+      <c r="C527" s="4" t="n"/>
+    </row>
+    <row r="528">
+      <c r="C528" s="4" t="n"/>
+    </row>
+    <row r="529">
+      <c r="C529" s="4" t="n"/>
+    </row>
+    <row r="530">
+      <c r="C530" s="4" t="n"/>
+    </row>
+    <row r="531">
+      <c r="C531" s="4" t="n"/>
+    </row>
+    <row r="532">
+      <c r="C532" s="4" t="n"/>
+    </row>
+    <row r="533">
+      <c r="C533" s="4" t="n"/>
+    </row>
+    <row r="534">
+      <c r="C534" s="4" t="n"/>
+    </row>
+    <row r="535">
+      <c r="C535" s="4" t="n"/>
+    </row>
+    <row r="536">
+      <c r="C536" s="4" t="n"/>
+    </row>
+    <row r="537">
+      <c r="C537" s="4" t="n"/>
+    </row>
+    <row r="538">
+      <c r="C538" s="4" t="n"/>
+    </row>
+    <row r="539">
+      <c r="C539" s="4" t="n"/>
+    </row>
+    <row r="540">
+      <c r="C540" s="4" t="n"/>
+    </row>
+    <row r="541">
+      <c r="C541" s="4" t="n"/>
+    </row>
+    <row r="542">
+      <c r="C542" s="4" t="n"/>
+    </row>
+    <row r="543">
+      <c r="C543" s="4" t="n"/>
+    </row>
+    <row r="544">
+      <c r="C544" s="4" t="n"/>
+    </row>
+    <row r="545">
+      <c r="C545" s="4" t="n"/>
+    </row>
+    <row r="546">
+      <c r="C546" s="4" t="n"/>
+    </row>
+    <row r="547">
+      <c r="C547" s="4" t="n"/>
+    </row>
+    <row r="548">
+      <c r="C548" s="4" t="n"/>
+    </row>
+    <row r="549">
+      <c r="C549" s="4" t="n"/>
+    </row>
+    <row r="550">
+      <c r="C550" s="4" t="n"/>
+    </row>
+    <row r="551">
+      <c r="C551" s="4" t="n"/>
+    </row>
+    <row r="552">
+      <c r="C552" s="4" t="n"/>
+    </row>
+    <row r="553">
+      <c r="C553" s="4" t="n"/>
+    </row>
+    <row r="554">
+      <c r="C554" s="4" t="n"/>
+    </row>
+    <row r="555">
+      <c r="C555" s="4" t="n"/>
+    </row>
+    <row r="556">
+      <c r="C556" s="4" t="n"/>
+    </row>
+    <row r="557">
+      <c r="C557" s="4" t="n"/>
+    </row>
+    <row r="558">
+      <c r="C558" s="4" t="n"/>
+    </row>
+    <row r="559">
+      <c r="C559" s="4" t="n"/>
+    </row>
+    <row r="560">
+      <c r="C560" s="4" t="n"/>
+    </row>
+    <row r="561">
+      <c r="C561" s="4" t="n"/>
+    </row>
+    <row r="562">
+      <c r="C562" s="4" t="n"/>
+    </row>
+    <row r="563">
+      <c r="C563" s="4" t="n"/>
+    </row>
+    <row r="564">
+      <c r="C564" s="4" t="n"/>
+    </row>
+    <row r="565">
+      <c r="C565" s="4" t="n"/>
+    </row>
+    <row r="566">
+      <c r="C566" s="4" t="n"/>
+    </row>
+    <row r="567">
+      <c r="C567" s="4" t="n"/>
+    </row>
+    <row r="568">
+      <c r="C568" s="4" t="n"/>
+    </row>
+    <row r="569">
+      <c r="C569" s="4" t="n"/>
+    </row>
+    <row r="570">
+      <c r="C570" s="4" t="n"/>
+    </row>
+    <row r="571">
+      <c r="C571" s="4" t="n"/>
+    </row>
+    <row r="572">
+      <c r="C572" s="4" t="n"/>
+    </row>
+    <row r="573">
+      <c r="C573" s="4" t="n"/>
+    </row>
+    <row r="574">
+      <c r="C574" s="4" t="n"/>
+    </row>
+    <row r="575">
+      <c r="C575" s="4" t="n"/>
+    </row>
+    <row r="576">
+      <c r="C576" s="4" t="n"/>
+    </row>
+    <row r="577">
+      <c r="C577" s="4" t="n"/>
+    </row>
+    <row r="578">
+      <c r="C578" s="4" t="n"/>
+    </row>
+    <row r="579">
+      <c r="C579" s="4" t="n"/>
+    </row>
+    <row r="580">
+      <c r="C580" s="4" t="n"/>
+    </row>
+    <row r="581">
+      <c r="C581" s="4" t="n"/>
+    </row>
+    <row r="582">
+      <c r="C582" s="4" t="n"/>
+    </row>
+    <row r="583">
+      <c r="C583" s="4" t="n"/>
+    </row>
+    <row r="584">
+      <c r="C584" s="4" t="n"/>
+    </row>
+    <row r="585">
+      <c r="C585" s="4" t="n"/>
+    </row>
+    <row r="586">
+      <c r="C586" s="4" t="n"/>
+    </row>
+    <row r="587">
+      <c r="C587" s="4" t="n"/>
+    </row>
+    <row r="588">
+      <c r="C588" s="4" t="n"/>
+    </row>
+    <row r="589">
+      <c r="C589" s="4" t="n"/>
+    </row>
+    <row r="590">
+      <c r="C590" s="4" t="n"/>
+    </row>
+    <row r="591">
+      <c r="C591" s="4" t="n"/>
+    </row>
+    <row r="592">
+      <c r="C592" s="4" t="n"/>
+    </row>
+    <row r="593">
+      <c r="C593" s="4" t="n"/>
+    </row>
+    <row r="594">
+      <c r="C594" s="4" t="n"/>
+    </row>
+    <row r="595">
+      <c r="C595" s="4" t="n"/>
+    </row>
+    <row r="596">
+      <c r="C596" s="4" t="n"/>
+    </row>
+    <row r="597">
+      <c r="C597" s="4" t="n"/>
+    </row>
+    <row r="598">
+      <c r="C598" s="4" t="n"/>
+    </row>
+    <row r="599">
+      <c r="C599" s="4" t="n"/>
+    </row>
+    <row r="600">
+      <c r="C600" s="4" t="n"/>
+    </row>
+    <row r="601">
+      <c r="C601" s="4" t="n"/>
+    </row>
+    <row r="602">
+      <c r="C602" s="4" t="n"/>
+    </row>
+    <row r="603">
+      <c r="C603" s="4" t="n"/>
+    </row>
+    <row r="604">
+      <c r="C604" s="4" t="n"/>
+    </row>
+    <row r="605">
+      <c r="C605" s="4" t="n"/>
+    </row>
+    <row r="606">
+      <c r="C606" s="4" t="n"/>
+    </row>
+    <row r="607">
+      <c r="C607" s="4" t="n"/>
+    </row>
+    <row r="608">
+      <c r="C608" s="4" t="n"/>
+    </row>
+    <row r="609">
+      <c r="C609" s="4" t="n"/>
+    </row>
+    <row r="610">
+      <c r="C610" s="4" t="n"/>
+    </row>
+    <row r="611">
+      <c r="C611" s="4" t="n"/>
+    </row>
+    <row r="612">
+      <c r="C612" s="4" t="n"/>
+    </row>
+    <row r="613">
+      <c r="C613" s="4" t="n"/>
+    </row>
+    <row r="614">
+      <c r="C614" s="4" t="n"/>
+    </row>
+    <row r="615">
+      <c r="C615" s="4" t="n"/>
+    </row>
+    <row r="616">
+      <c r="C616" s="4" t="n"/>
+    </row>
+    <row r="617">
+      <c r="C617" s="4" t="n"/>
+    </row>
+    <row r="618">
+      <c r="C618" s="4" t="n"/>
+    </row>
+    <row r="619">
+      <c r="C619" s="4" t="n"/>
+    </row>
+    <row r="620">
+      <c r="C620" s="4" t="n"/>
+    </row>
+    <row r="621">
+      <c r="C621" s="4" t="n"/>
+    </row>
+    <row r="622">
+      <c r="C622" s="4" t="n"/>
+    </row>
+    <row r="623">
+      <c r="C623" s="4" t="n"/>
+    </row>
+    <row r="624">
+      <c r="C624" s="4" t="n"/>
+    </row>
+    <row r="625">
+      <c r="C625" s="4" t="n"/>
+    </row>
+    <row r="626">
+      <c r="C626" s="4" t="n"/>
+    </row>
+    <row r="627">
+      <c r="C627" s="4" t="n"/>
+    </row>
+    <row r="628">
+      <c r="C628" s="4" t="n"/>
+    </row>
+    <row r="629">
+      <c r="C629" s="4" t="n"/>
+    </row>
+    <row r="630">
+      <c r="C630" s="4" t="n"/>
+    </row>
+    <row r="631">
+      <c r="C631" s="4" t="n"/>
+    </row>
+    <row r="632">
+      <c r="C632" s="4" t="n"/>
+    </row>
+    <row r="633">
+      <c r="C633" s="4" t="n"/>
+    </row>
+    <row r="634">
+      <c r="C634" s="4" t="n"/>
+    </row>
+    <row r="635">
+      <c r="C635" s="4" t="n"/>
+    </row>
+    <row r="636">
+      <c r="C636" s="4" t="n"/>
+    </row>
+    <row r="637">
+      <c r="C637" s="4" t="n"/>
+    </row>
+    <row r="638">
+      <c r="C638" s="4" t="n"/>
+    </row>
+    <row r="639">
+      <c r="C639" s="4" t="n"/>
+    </row>
+    <row r="640">
+      <c r="C640" s="4" t="n"/>
+    </row>
+    <row r="641">
+      <c r="C641" s="4" t="n"/>
+    </row>
+    <row r="642">
+      <c r="C642" s="4" t="n"/>
+    </row>
+    <row r="643">
+      <c r="C643" s="4" t="n"/>
+    </row>
+    <row r="644">
+      <c r="C644" s="4" t="n"/>
+    </row>
+    <row r="645">
+      <c r="C645" s="4" t="n"/>
+    </row>
+    <row r="646">
+      <c r="C646" s="4" t="n"/>
+    </row>
+    <row r="647">
+      <c r="C647" s="4" t="n"/>
+    </row>
+    <row r="648">
+      <c r="C648" s="4" t="n"/>
+    </row>
+    <row r="649">
+      <c r="C649" s="4" t="n"/>
+    </row>
+    <row r="650">
+      <c r="C650" s="4" t="n"/>
+    </row>
+    <row r="651">
+      <c r="C651" s="4" t="n"/>
+    </row>
+    <row r="652">
+      <c r="C652" s="4" t="n"/>
+    </row>
+    <row r="653">
+      <c r="C653" s="4" t="n"/>
+    </row>
+    <row r="654">
+      <c r="C654" s="4" t="n"/>
+    </row>
+    <row r="655">
+      <c r="C655" s="4" t="n"/>
+    </row>
+    <row r="656">
+      <c r="C656" s="4" t="n"/>
+    </row>
+    <row r="657">
+      <c r="C657" s="4" t="n"/>
+    </row>
+    <row r="658">
+      <c r="C658" s="4" t="n"/>
+    </row>
+    <row r="659">
+      <c r="C659" s="4" t="n"/>
+    </row>
+    <row r="660">
+      <c r="C660" s="4" t="n"/>
+    </row>
+    <row r="661">
+      <c r="C661" s="4" t="n"/>
+    </row>
+    <row r="662">
+      <c r="C662" s="4" t="n"/>
+    </row>
+    <row r="663">
+      <c r="C663" s="4" t="n"/>
+    </row>
+    <row r="664">
+      <c r="C664" s="4" t="n"/>
+    </row>
+    <row r="665">
+      <c r="C665" s="4" t="n"/>
+    </row>
+    <row r="666">
+      <c r="C666" s="4" t="n"/>
+    </row>
+    <row r="667">
+      <c r="C667" s="4" t="n"/>
+    </row>
+    <row r="668">
+      <c r="C668" s="4" t="n"/>
+    </row>
+    <row r="669">
+      <c r="C669" s="4" t="n"/>
+    </row>
+    <row r="670">
+      <c r="C670" s="4" t="n"/>
+    </row>
+    <row r="671">
+      <c r="C671" s="4" t="n"/>
+    </row>
+    <row r="672">
+      <c r="C672" s="4" t="n"/>
+    </row>
+    <row r="673">
+      <c r="C673" s="4" t="n"/>
+    </row>
+    <row r="674">
+      <c r="C674" s="4" t="n"/>
+    </row>
+    <row r="675">
+      <c r="C675" s="4" t="n"/>
+    </row>
+    <row r="676">
+      <c r="C676" s="4" t="n"/>
+    </row>
+    <row r="677">
+      <c r="C677" s="4" t="n"/>
+    </row>
+    <row r="678">
+      <c r="C678" s="4" t="n"/>
+    </row>
+    <row r="679">
+      <c r="C679" s="4" t="n"/>
+    </row>
+    <row r="680">
+      <c r="C680" s="4" t="n"/>
+    </row>
+    <row r="681">
+      <c r="C681" s="4" t="n"/>
+    </row>
+    <row r="682">
+      <c r="C682" s="4" t="n"/>
+    </row>
+    <row r="683">
+      <c r="C683" s="4" t="n"/>
+    </row>
+    <row r="684">
+      <c r="C684" s="4" t="n"/>
+    </row>
+    <row r="685">
+      <c r="C685" s="4" t="n"/>
+    </row>
+    <row r="686">
+      <c r="C686" s="4" t="n"/>
+    </row>
+    <row r="687">
+      <c r="C687" s="4" t="n"/>
+    </row>
+    <row r="688">
+      <c r="C688" s="4" t="n"/>
+    </row>
+    <row r="689">
+      <c r="C689" s="4" t="n"/>
+    </row>
+    <row r="690">
+      <c r="C690" s="4" t="n"/>
+    </row>
+    <row r="691">
+      <c r="C691" s="4" t="n"/>
+    </row>
+    <row r="692">
+      <c r="C692" s="4" t="n"/>
+    </row>
+    <row r="693">
+      <c r="C693" s="4" t="n"/>
+    </row>
+    <row r="694">
+      <c r="C694" s="4" t="n"/>
+    </row>
+    <row r="695">
+      <c r="C695" s="4" t="n"/>
+    </row>
+    <row r="696">
+      <c r="C696" s="4" t="n"/>
+    </row>
+    <row r="697">
+      <c r="C697" s="4" t="n"/>
+    </row>
+    <row r="698">
+      <c r="C698" s="4" t="n"/>
+    </row>
+    <row r="699">
+      <c r="C699" s="4" t="n"/>
+    </row>
+    <row r="700">
+      <c r="C700" s="4" t="n"/>
+    </row>
+    <row r="701">
+      <c r="C701" s="4" t="n"/>
+    </row>
+    <row r="702">
+      <c r="C702" s="4" t="n"/>
+    </row>
+    <row r="703">
+      <c r="C703" s="4" t="n"/>
+    </row>
+    <row r="704">
+      <c r="C704" s="4" t="n"/>
+    </row>
+    <row r="705">
+      <c r="C705" s="4" t="n"/>
+    </row>
+    <row r="706">
+      <c r="C706" s="4" t="n"/>
+    </row>
+    <row r="707">
+      <c r="C707" s="4" t="n"/>
+    </row>
+    <row r="708">
+      <c r="C708" s="4" t="n"/>
+    </row>
+    <row r="709">
+      <c r="C709" s="4" t="n"/>
+    </row>
+    <row r="710">
+      <c r="C710" s="4" t="n"/>
+    </row>
+    <row r="711">
+      <c r="C711" s="4" t="n"/>
+    </row>
+    <row r="712">
+      <c r="C712" s="4" t="n"/>
+    </row>
+    <row r="713">
+      <c r="C713" s="4" t="n"/>
+    </row>
+    <row r="714">
+      <c r="C714" s="4" t="n"/>
+    </row>
+    <row r="715">
+      <c r="C715" s="4" t="n"/>
+    </row>
+    <row r="716">
+      <c r="C716" s="4" t="n"/>
+    </row>
+    <row r="717">
+      <c r="C717" s="4" t="n"/>
+    </row>
+    <row r="718">
+      <c r="C718" s="4" t="n"/>
+    </row>
+    <row r="719">
+      <c r="C719" s="4" t="n"/>
+    </row>
+    <row r="720">
+      <c r="C720" s="4" t="n"/>
+    </row>
+    <row r="721">
+      <c r="C721" s="4" t="n"/>
+    </row>
+    <row r="722">
+      <c r="C722" s="4" t="n"/>
+    </row>
+    <row r="723">
+      <c r="C723" s="4" t="n"/>
+    </row>
+    <row r="724">
+      <c r="C724" s="4" t="n"/>
+    </row>
+    <row r="725">
+      <c r="C725" s="4" t="n"/>
+    </row>
+    <row r="726">
+      <c r="C726" s="4" t="n"/>
+    </row>
+    <row r="727">
+      <c r="C727" s="4" t="n"/>
+    </row>
+    <row r="728">
+      <c r="C728" s="4" t="n"/>
+    </row>
+    <row r="729">
+      <c r="C729" s="4" t="n"/>
+    </row>
+    <row r="730">
+      <c r="C730" s="4" t="n"/>
+    </row>
+    <row r="731">
+      <c r="C731" s="4" t="n"/>
+    </row>
+    <row r="732">
+      <c r="C732" s="4" t="n"/>
+    </row>
+    <row r="733">
+      <c r="C733" s="4" t="n"/>
+    </row>
+    <row r="734">
+      <c r="C734" s="4" t="n"/>
+    </row>
+    <row r="735">
+      <c r="C735" s="4" t="n"/>
+    </row>
+    <row r="736">
+      <c r="C736" s="4" t="n"/>
+    </row>
+    <row r="737">
+      <c r="C737" s="4" t="n"/>
+    </row>
+    <row r="738">
+      <c r="C738" s="4" t="n"/>
+    </row>
+    <row r="739">
+      <c r="C739" s="4" t="n"/>
+    </row>
+    <row r="740">
+      <c r="C740" s="4" t="n"/>
+    </row>
+    <row r="741">
+      <c r="C741" s="4" t="n"/>
+    </row>
+    <row r="742">
+      <c r="C742" s="4" t="n"/>
+    </row>
+    <row r="743">
+      <c r="C743" s="4" t="n"/>
+    </row>
+    <row r="744">
+      <c r="C744" s="4" t="n"/>
+    </row>
+    <row r="745">
+      <c r="C745" s="4" t="n"/>
+    </row>
+    <row r="746">
+      <c r="C746" s="4" t="n"/>
+    </row>
+    <row r="747">
+      <c r="C747" s="4" t="n"/>
+    </row>
+    <row r="748">
+      <c r="C748" s="4" t="n"/>
+    </row>
+    <row r="749">
+      <c r="C749" s="4" t="n"/>
+    </row>
+    <row r="750">
+      <c r="C750" s="4" t="n"/>
+    </row>
+    <row r="751">
+      <c r="C751" s="4" t="n"/>
+    </row>
+    <row r="752">
+      <c r="C752" s="4" t="n"/>
+    </row>
+    <row r="753">
+      <c r="C753" s="4" t="n"/>
+    </row>
+    <row r="754">
+      <c r="C754" s="4" t="n"/>
+    </row>
+    <row r="755">
+      <c r="C755" s="4" t="n"/>
+    </row>
+    <row r="756">
+      <c r="C756" s="4" t="n"/>
+    </row>
+    <row r="757">
+      <c r="C757" s="4" t="n"/>
+    </row>
+    <row r="758">
+      <c r="C758" s="4" t="n"/>
+    </row>
+    <row r="759">
+      <c r="C759" s="4" t="n"/>
+    </row>
+    <row r="760">
+      <c r="C760" s="4" t="n"/>
+    </row>
+    <row r="761">
+      <c r="C761" s="4" t="n"/>
+    </row>
+    <row r="762">
+      <c r="C762" s="4" t="n"/>
+    </row>
+    <row r="763">
+      <c r="C763" s="4" t="n"/>
+    </row>
+    <row r="764">
+      <c r="C764" s="4" t="n"/>
+    </row>
+    <row r="765">
+      <c r="C765" s="4" t="n"/>
+    </row>
+    <row r="766">
+      <c r="C766" s="4" t="n"/>
+    </row>
+    <row r="767">
+      <c r="C767" s="4" t="n"/>
+    </row>
+    <row r="768">
+      <c r="C768" s="4" t="n"/>
+    </row>
+    <row r="769">
+      <c r="C769" s="4" t="n"/>
+    </row>
+    <row r="770">
+      <c r="C770" s="4" t="n"/>
+    </row>
+    <row r="771">
+      <c r="C771" s="4" t="n"/>
+    </row>
+    <row r="772">
+      <c r="C772" s="4" t="n"/>
+    </row>
+    <row r="773">
+      <c r="C773" s="4" t="n"/>
+    </row>
+    <row r="774">
+      <c r="C774" s="4" t="n"/>
+    </row>
+    <row r="775">
+      <c r="C775" s="4" t="n"/>
+    </row>
+    <row r="776">
+      <c r="C776" s="4" t="n"/>
+    </row>
+    <row r="777">
+      <c r="C777" s="4" t="n"/>
+    </row>
+    <row r="778">
+      <c r="C778" s="4" t="n"/>
+    </row>
+    <row r="779">
+      <c r="C779" s="4" t="n"/>
+    </row>
+    <row r="780">
+      <c r="C780" s="4" t="n"/>
+    </row>
+    <row r="781">
+      <c r="C781" s="4" t="n"/>
+    </row>
+    <row r="782">
+      <c r="C782" s="4" t="n"/>
+    </row>
+    <row r="783">
+      <c r="C783" s="4" t="n"/>
+    </row>
+    <row r="784">
+      <c r="C784" s="4" t="n"/>
+    </row>
+    <row r="785">
+      <c r="C785" s="4" t="n"/>
+    </row>
+    <row r="786">
+      <c r="C786" s="4" t="n"/>
+    </row>
+    <row r="787">
+      <c r="C787" s="4" t="n"/>
+    </row>
+    <row r="788">
+      <c r="C788" s="4" t="n"/>
+    </row>
+    <row r="789">
+      <c r="C789" s="4" t="n"/>
+    </row>
+    <row r="790">
+      <c r="C790" s="4" t="n"/>
+    </row>
+    <row r="791">
+      <c r="C791" s="4" t="n"/>
+    </row>
+    <row r="792">
+      <c r="C792" s="4" t="n"/>
+    </row>
+    <row r="793">
+      <c r="C793" s="4" t="n"/>
+    </row>
+    <row r="794">
+      <c r="C794" s="4" t="n"/>
+    </row>
+    <row r="795">
+      <c r="C795" s="4" t="n"/>
+    </row>
+    <row r="796">
+      <c r="C796" s="4" t="n"/>
+    </row>
+    <row r="797">
+      <c r="C797" s="4" t="n"/>
+    </row>
+    <row r="798">
+      <c r="C798" s="4" t="n"/>
+    </row>
+    <row r="799">
+      <c r="C799" s="4" t="n"/>
+    </row>
+    <row r="800">
+      <c r="C800" s="4" t="n"/>
+    </row>
+    <row r="801">
+      <c r="C801" s="4" t="n"/>
+    </row>
+    <row r="802">
+      <c r="C802" s="4" t="n"/>
+    </row>
+    <row r="803">
+      <c r="C803" s="4" t="n"/>
+    </row>
+    <row r="804">
+      <c r="C804" s="4" t="n"/>
+    </row>
+    <row r="805">
+      <c r="C805" s="4" t="n"/>
+    </row>
+    <row r="806">
+      <c r="C806" s="4" t="n"/>
+    </row>
+    <row r="807">
+      <c r="C807" s="4" t="n"/>
+    </row>
+    <row r="808">
+      <c r="C808" s="4" t="n"/>
+    </row>
+    <row r="809">
+      <c r="C809" s="4" t="n"/>
+    </row>
+    <row r="810">
+      <c r="C810" s="4" t="n"/>
+    </row>
+    <row r="811">
+      <c r="C811" s="4" t="n"/>
+    </row>
+    <row r="812">
+      <c r="C812" s="4" t="n"/>
+    </row>
+    <row r="813">
+      <c r="C813" s="4" t="n"/>
+    </row>
+    <row r="814">
+      <c r="C814" s="4" t="n"/>
+    </row>
+    <row r="815">
+      <c r="C815" s="4" t="n"/>
+    </row>
+    <row r="816">
+      <c r="C816" s="4" t="n"/>
+    </row>
+    <row r="817">
+      <c r="C817" s="4" t="n"/>
+    </row>
+    <row r="818">
+      <c r="C818" s="4" t="n"/>
+    </row>
+    <row r="819">
+      <c r="C819" s="4" t="n"/>
+    </row>
+    <row r="820">
+      <c r="C820" s="4" t="n"/>
+    </row>
+    <row r="821">
+      <c r="C821" s="4" t="n"/>
+    </row>
+    <row r="822">
+      <c r="C822" s="4" t="n"/>
+    </row>
+    <row r="823">
+      <c r="C823" s="4" t="n"/>
+    </row>
+    <row r="824">
+      <c r="C824" s="4" t="n"/>
+    </row>
+    <row r="825">
+      <c r="C825" s="4" t="n"/>
+    </row>
+    <row r="826">
+      <c r="C826" s="4" t="n"/>
+    </row>
+    <row r="827">
+      <c r="C827" s="4" t="n"/>
+    </row>
+    <row r="828">
+      <c r="C828" s="4" t="n"/>
+    </row>
+    <row r="829">
+      <c r="C829" s="4" t="n"/>
+    </row>
+    <row r="830">
+      <c r="C830" s="4" t="n"/>
+    </row>
+    <row r="831">
+      <c r="C831" s="4" t="n"/>
+    </row>
+    <row r="832">
+      <c r="C832" s="4" t="n"/>
+    </row>
+    <row r="833">
+      <c r="C833" s="4" t="n"/>
+    </row>
+    <row r="834">
+      <c r="C834" s="4" t="n"/>
+    </row>
+    <row r="835">
+      <c r="C835" s="4" t="n"/>
+    </row>
+    <row r="836">
+      <c r="C836" s="4" t="n"/>
+    </row>
+    <row r="837">
+      <c r="C837" s="4" t="n"/>
+    </row>
+    <row r="838">
+      <c r="C838" s="4" t="n"/>
+    </row>
+    <row r="839">
+      <c r="C839" s="4" t="n"/>
+    </row>
+    <row r="840">
+      <c r="C840" s="4" t="n"/>
+    </row>
+    <row r="841">
+      <c r="C841" s="4" t="n"/>
+    </row>
+    <row r="842">
+      <c r="C842" s="4" t="n"/>
+    </row>
+    <row r="843">
+      <c r="C843" s="4" t="n"/>
+    </row>
+    <row r="844">
+      <c r="C844" s="4" t="n"/>
+    </row>
+    <row r="845">
+      <c r="C845" s="4" t="n"/>
+    </row>
+    <row r="846">
+      <c r="C846" s="4" t="n"/>
+    </row>
+    <row r="847">
+      <c r="C847" s="4" t="n"/>
+    </row>
+    <row r="848">
+      <c r="C848" s="4" t="n"/>
+    </row>
+    <row r="849">
+      <c r="C849" s="4" t="n"/>
+    </row>
+    <row r="850">
+      <c r="C850" s="4" t="n"/>
+    </row>
+    <row r="851">
+      <c r="C851" s="4" t="n"/>
+    </row>
+    <row r="852">
+      <c r="C852" s="4" t="n"/>
+    </row>
+    <row r="853">
+      <c r="C853" s="4" t="n"/>
+    </row>
+    <row r="854">
+      <c r="C854" s="4" t="n"/>
+    </row>
+    <row r="855">
+      <c r="C855" s="4" t="n"/>
+    </row>
+    <row r="856">
+      <c r="C856" s="4" t="n"/>
+    </row>
+    <row r="857">
+      <c r="C857" s="4" t="n"/>
+    </row>
+    <row r="858">
+      <c r="C858" s="4" t="n"/>
+    </row>
+    <row r="859">
+      <c r="C859" s="4" t="n"/>
+    </row>
+    <row r="860">
+      <c r="C860" s="4" t="n"/>
+    </row>
+    <row r="861">
+      <c r="C861" s="4" t="n"/>
+    </row>
+    <row r="862">
+      <c r="C862" s="4" t="n"/>
+    </row>
+    <row r="863">
+      <c r="C863" s="4" t="n"/>
+    </row>
+    <row r="864">
+      <c r="C864" s="4" t="n"/>
+    </row>
+    <row r="865">
+      <c r="C865" s="4" t="n"/>
+    </row>
+    <row r="866">
+      <c r="C866" s="4" t="n"/>
+    </row>
+    <row r="867">
+      <c r="C867" s="4" t="n"/>
+    </row>
+    <row r="868">
+      <c r="C868" s="4" t="n"/>
+    </row>
+    <row r="869">
+      <c r="C869" s="4" t="n"/>
+    </row>
+    <row r="870">
+      <c r="C870" s="4" t="n"/>
+    </row>
+    <row r="871">
+      <c r="C871" s="4" t="n"/>
+    </row>
+    <row r="872">
+      <c r="C872" s="4" t="n"/>
+    </row>
+    <row r="873">
+      <c r="C873" s="4" t="n"/>
+    </row>
+    <row r="874">
+      <c r="C874" s="4" t="n"/>
+    </row>
+    <row r="875">
+      <c r="C875" s="4" t="n"/>
+    </row>
+    <row r="876">
+      <c r="C876" s="4" t="n"/>
+    </row>
+    <row r="877">
+      <c r="C877" s="4" t="n"/>
+    </row>
+    <row r="878">
+      <c r="C878" s="4" t="n"/>
+    </row>
+    <row r="879">
+      <c r="C879" s="4" t="n"/>
+    </row>
+    <row r="880">
+      <c r="C880" s="4" t="n"/>
+    </row>
+    <row r="881">
+      <c r="C881" s="4" t="n"/>
+    </row>
+    <row r="882">
+      <c r="C882" s="4" t="n"/>
+    </row>
+    <row r="883">
+      <c r="C883" s="4" t="n"/>
+    </row>
+    <row r="884">
+      <c r="C884" s="4" t="n"/>
+    </row>
+    <row r="885">
+      <c r="C885" s="4" t="n"/>
+    </row>
+    <row r="886">
+      <c r="C886" s="4" t="n"/>
+    </row>
+    <row r="887">
+      <c r="C887" s="4" t="n"/>
+    </row>
+    <row r="888">
+      <c r="C888" s="4" t="n"/>
+    </row>
+    <row r="889">
+      <c r="C889" s="4" t="n"/>
+    </row>
+    <row r="890">
+      <c r="C890" s="4" t="n"/>
+    </row>
+    <row r="891">
+      <c r="C891" s="4" t="n"/>
+    </row>
+    <row r="892">
+      <c r="C892" s="4" t="n"/>
+    </row>
+    <row r="893">
+      <c r="C893" s="4" t="n"/>
+    </row>
+    <row r="894">
+      <c r="C894" s="4" t="n"/>
+    </row>
+    <row r="895">
+      <c r="C895" s="4" t="n"/>
+    </row>
+    <row r="896">
+      <c r="C896" s="4" t="n"/>
+    </row>
+    <row r="897">
+      <c r="C897" s="4" t="n"/>
+    </row>
+    <row r="898">
+      <c r="C898" s="4" t="n"/>
+    </row>
+    <row r="899">
+      <c r="C899" s="4" t="n"/>
+    </row>
+    <row r="900">
+      <c r="C900" s="4" t="n"/>
+    </row>
+    <row r="901">
+      <c r="C901" s="4" t="n"/>
+    </row>
+    <row r="902">
+      <c r="C902" s="4" t="n"/>
+    </row>
+    <row r="903">
+      <c r="C903" s="4" t="n"/>
+    </row>
+    <row r="904">
+      <c r="C904" s="4" t="n"/>
+    </row>
+    <row r="905">
+      <c r="C905" s="4" t="n"/>
+    </row>
+    <row r="906">
+      <c r="C906" s="4" t="n"/>
+    </row>
+    <row r="907">
+      <c r="C907" s="4" t="n"/>
+    </row>
+    <row r="908">
+      <c r="C908" s="4" t="n"/>
+    </row>
+    <row r="909">
+      <c r="C909" s="4" t="n"/>
+    </row>
+    <row r="910">
+      <c r="C910" s="4" t="n"/>
+    </row>
+    <row r="911">
+      <c r="C911" s="4" t="n"/>
+    </row>
+    <row r="912">
+      <c r="C912" s="4" t="n"/>
+    </row>
+    <row r="913">
+      <c r="C913" s="4" t="n"/>
+    </row>
+    <row r="914">
+      <c r="C914" s="4" t="n"/>
+    </row>
+    <row r="915">
+      <c r="C915" s="4" t="n"/>
+    </row>
+    <row r="916">
+      <c r="C916" s="4" t="n"/>
+    </row>
+    <row r="917">
+      <c r="C917" s="4" t="n"/>
+    </row>
+    <row r="918">
+      <c r="C918" s="4" t="n"/>
+    </row>
+    <row r="919">
+      <c r="C919" s="4" t="n"/>
+    </row>
+    <row r="920">
+      <c r="C920" s="4" t="n"/>
+    </row>
+    <row r="921">
+      <c r="C921" s="4" t="n"/>
+    </row>
+    <row r="922">
+      <c r="C922" s="4" t="n"/>
+    </row>
+    <row r="923">
+      <c r="C923" s="4" t="n"/>
+    </row>
+    <row r="924">
+      <c r="C924" s="4" t="n"/>
+    </row>
+    <row r="925">
+      <c r="C925" s="4" t="n"/>
+    </row>
+    <row r="926">
+      <c r="C926" s="4" t="n"/>
+    </row>
+    <row r="927">
+      <c r="C927" s="4" t="n"/>
+    </row>
+    <row r="928">
+      <c r="C928" s="4" t="n"/>
+    </row>
+    <row r="929">
+      <c r="C929" s="4" t="n"/>
+    </row>
+    <row r="930">
+      <c r="C930" s="4" t="n"/>
+    </row>
+    <row r="931">
+      <c r="C931" s="4" t="n"/>
+    </row>
+    <row r="932">
+      <c r="C932" s="4" t="n"/>
+    </row>
+    <row r="933">
+      <c r="C933" s="4" t="n"/>
+    </row>
+    <row r="934">
+      <c r="C934" s="4" t="n"/>
+    </row>
+    <row r="935">
+      <c r="C935" s="4" t="n"/>
+    </row>
+    <row r="936">
+      <c r="C936" s="4" t="n"/>
+    </row>
+    <row r="937">
+      <c r="C937" s="4" t="n"/>
+    </row>
+    <row r="938">
+      <c r="C938" s="4" t="n"/>
+    </row>
+    <row r="939">
+      <c r="C939" s="4" t="n"/>
+    </row>
+    <row r="940">
+      <c r="C940" s="4" t="n"/>
+    </row>
+    <row r="941">
+      <c r="C941" s="4" t="n"/>
+    </row>
+    <row r="942">
+      <c r="C942" s="4" t="n"/>
+    </row>
+    <row r="943">
+      <c r="C943" s="4" t="n"/>
+    </row>
+    <row r="944">
+      <c r="C944" s="4" t="n"/>
+    </row>
+    <row r="945">
+      <c r="C945" s="4" t="n"/>
+    </row>
+    <row r="946">
+      <c r="C946" s="4" t="n"/>
+    </row>
+    <row r="947">
+      <c r="C947" s="4" t="n"/>
+    </row>
+    <row r="948">
+      <c r="C948" s="4" t="n"/>
+    </row>
+    <row r="949">
+      <c r="C949" s="4" t="n"/>
+    </row>
+    <row r="950">
+      <c r="C950" s="4" t="n"/>
+    </row>
+    <row r="951">
+      <c r="C951" s="4" t="n"/>
+    </row>
+    <row r="952">
+      <c r="C952" s="4" t="n"/>
+    </row>
+    <row r="953">
+      <c r="C953" s="4" t="n"/>
+    </row>
+    <row r="954">
+      <c r="C954" s="4" t="n"/>
+    </row>
+    <row r="955">
+      <c r="C955" s="4" t="n"/>
+    </row>
+    <row r="956">
+      <c r="C956" s="4" t="n"/>
+    </row>
+    <row r="957">
+      <c r="C957" s="4" t="n"/>
+    </row>
+    <row r="958">
+      <c r="C958" s="4" t="n"/>
+    </row>
+    <row r="959">
+      <c r="C959" s="4" t="n"/>
+    </row>
+    <row r="960">
+      <c r="C960" s="4" t="n"/>
+    </row>
+    <row r="961">
+      <c r="C961" s="4" t="n"/>
+    </row>
+    <row r="962">
+      <c r="C962" s="4" t="n"/>
+    </row>
+    <row r="963">
+      <c r="C963" s="4" t="n"/>
+    </row>
+    <row r="964">
+      <c r="C964" s="4" t="n"/>
+    </row>
+    <row r="965">
+      <c r="C965" s="4" t="n"/>
+    </row>
+    <row r="966">
+      <c r="C966" s="4" t="n"/>
+    </row>
+    <row r="967">
+      <c r="C967" s="4" t="n"/>
+    </row>
+    <row r="968">
+      <c r="C968" s="4" t="n"/>
+    </row>
+    <row r="969">
+      <c r="C969" s="4" t="n"/>
+    </row>
+    <row r="970">
+      <c r="C970" s="4" t="n"/>
+    </row>
+    <row r="971">
+      <c r="C971" s="4" t="n"/>
+    </row>
+    <row r="972">
+      <c r="C972" s="4" t="n"/>
+    </row>
+    <row r="973">
+      <c r="C973" s="4" t="n"/>
+    </row>
+    <row r="974">
+      <c r="C974" s="4" t="n"/>
+    </row>
+    <row r="975">
+      <c r="C975" s="4" t="n"/>
+    </row>
+    <row r="976">
+      <c r="C976" s="4" t="n"/>
+    </row>
+    <row r="977">
+      <c r="C977" s="4" t="n"/>
+    </row>
+    <row r="978">
+      <c r="C978" s="4" t="n"/>
+    </row>
+    <row r="979">
+      <c r="C979" s="4" t="n"/>
+    </row>
+    <row r="980">
+      <c r="C980" s="4" t="n"/>
+    </row>
+    <row r="981">
+      <c r="C981" s="4" t="n"/>
+    </row>
+    <row r="982">
+      <c r="C982" s="4" t="n"/>
+    </row>
+    <row r="983">
+      <c r="C983" s="4" t="n"/>
+    </row>
+    <row r="984">
+      <c r="C984" s="4" t="n"/>
+    </row>
+    <row r="985">
+      <c r="C985" s="4" t="n"/>
+    </row>
+    <row r="986">
+      <c r="C986" s="4" t="n"/>
+    </row>
+    <row r="987">
+      <c r="C987" s="4" t="n"/>
+    </row>
+    <row r="988">
+      <c r="C988" s="4" t="n"/>
+    </row>
+    <row r="989">
+      <c r="C989" s="4" t="n"/>
+    </row>
+    <row r="990">
+      <c r="C990" s="4" t="n"/>
+    </row>
+    <row r="991">
+      <c r="C991" s="4" t="n"/>
+    </row>
+    <row r="992">
+      <c r="C992" s="4" t="n"/>
+    </row>
+    <row r="993">
+      <c r="C993" s="4" t="n"/>
+    </row>
+    <row r="994">
+      <c r="C994" s="4" t="n"/>
+    </row>
+    <row r="995">
+      <c r="C995" s="4" t="n"/>
+    </row>
+    <row r="996">
+      <c r="C996" s="4" t="n"/>
+    </row>
+    <row r="997">
+      <c r="C997" s="4" t="n"/>
+    </row>
+    <row r="998">
+      <c r="C998" s="4" t="n"/>
+    </row>
+    <row r="999">
+      <c r="C999" s="4" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="C1000" s="4" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor invalido" error="Solo se permiten: MICRO, SMALL, MEDIUM, LARGE, XL" type="list">
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor invalido" error="Solo se permiten: MICRO, SMALL, MEDIUM, LARGE, XL" type="list">
       <formula1>"MICRO,SMALL,MEDIUM,LARGE,XL"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Categoria invalida" error="Usa uno de los slugs validos o crea la categoria primero en OPS." type="list">
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Categoria invalida" error="Usa uno de los slugs validos o crea la categoria primero en OPS." type="list">
       <formula1>"hamburguesas,pizzas,sushi,lacteos,bebidas,sandwicheria,golosinas,almacen,limpieza"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,3,6,10,20"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1155,10 +3770,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -1168,103 +3783,103 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Guia rapida - Importacion de productos</t>
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Guia rapida - Importacion de productos MOOVY</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Como usar este archivo</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>1. Cargas tus productos en la hoja 'Productos' (una fila por producto).</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>2. Archivo -&gt; Guardar como -&gt; CSV UTF-8 (delimitado por comas).</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>2. Pasa el cursor sobre cada encabezado (triangulo rojo) para ver la ayuda.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>3. Entra a OPS -&gt; Catalogo de Paquetes -&gt; Importar Productos.</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>3. Guarda como CSV UTF-8 antes de importar: Archivo -&gt; Guardar como -&gt; CSV UTF-8 (delimitado por comas).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>4. Subi el CSV y tira 'Simular (Dry Run)' antes de importar.</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>4. Sube el CSV en: OPS -&gt; Catalogo de Paquetes -&gt; Importar Productos.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>5. Si la simulacion se ve bien, tira 'Importar X productos'.</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>5. Tira 'Simular (Dry Run)' antes de importar en firme.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
+      <c r="A9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Limite: 500 productos por carga. Slugs duplicados se omiten.</t>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Limite: 500 productos por carga. Slugs duplicados se omiten automaticamente.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>packageCategory - valores validos</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>Peso max (g)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>Largo max (cm)</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Ancho max (cm)</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>Alto max (cm)</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>volumeScore</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>Vehiculos</t>
         </is>
@@ -1406,148 +4021,242 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>categorySlug - valores validos</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>hamburguesas</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>pizzas</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>sushi</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>lacteos</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>bebidas</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>sandwicheria</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>golosinas</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>almacen</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>limpieza</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>barcode - formato esperado</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>- EAN-13 (13 digitos) es el estandar en Argentina. Tambien se aceptan EAN-8, UPC-12, o codigos internos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>- Si el codigo tiene ceros a la izquierda (ej: '0012345678905'), la columna esta formateada como TEXTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  para que Excel no los elimine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>- Si el producto no tiene codigo de barras (ej: vianda, combo armado), dejar vacio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>imageUrl - flujo de carga de imagenes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>- Las imagenes NO se incluyen dentro del Excel. El Excel solo guarda la URL de la imagen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>- Las imagenes se almacenan en Cloudflare R2 (bucket de MOOVY).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>- Formato de URL: https://cdn.somosmoovy.com/products/{nombre-archivo}.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (o https://pub-{ACCOUNT_ID}.r2.dev/{key} si no hay dominio custom).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>- Formato recomendado de imagen: WebP o JPG, 1024x1024 px, &lt; 500 KB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>- Una sola imagen por producto (imagen principal). Secundarias se cargan desde el panel OPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>- Si el producto no tiene foto todavia, dejar vacio. Despues se puede editar desde el panel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>Notas importantes</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>- El importador NO acepta .xlsx. Guardar como CSV UTF-8 antes de subir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>- Las celdas con triangulo rojo en la esquina tienen un comentario con ayuda.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>- El importador acepta CSV UTF-8 (no .xlsx directo). Guardar como CSV antes de subir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>- Los campos maxWeight, maxLength/Width/HeightCm, volumeScore y allowedVehicles son informativos.</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  El producto se vincula por 'packageCategory' (MICRO/SMALL/etc.), que ya tiene esas reglas en DB.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>- Filas con nombre que empieza con GASEOSAS, TONICAS, AGUAS, BEBIDAS, JUGOS o ENERGIZANTES se</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  ignoran automaticamente (se consideran encabezados de seccion).</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
         <is>
           <t>- Los productos se crean como catalogo maestro (sin comercio asignado) para armar paquetes B2B.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A1:D1"/>
+  <mergeCells count="25">
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="A53:G53"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A44:G44"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="A45:G45"/>
     <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A38:G38"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A46:G46"/>
     <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
